--- a/eval/gold_scenarios/q1_exception_dc9_figure_mismatch_01.xlsx
+++ b/eval/gold_scenarios/q1_exception_dc9_figure_mismatch_01.xlsx
@@ -759,12 +759,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>&lt;attribute_A_description&gt;</t>
+          <t>Preparer signed off with date on the Checklist.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>&lt;attribute_A_toc_procedure&gt;</t>
+          <t>Inspect Checklist column F for preparer initials and date.</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>&lt;attribute_B_description&gt;</t>
+          <t>Independent reviewer signed off with date.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>&lt;attribute_B_toc_procedure&gt;</t>
+          <t>Inspect Checklist column G for reviewer initials and date.</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>&lt;attribute_C_description&gt;</t>
+          <t>Billing formulas tie to the underlying supporting schedules.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>&lt;attribute_C_toc_procedure&gt;</t>
+          <t>Recompute the billing total from the supporting schedule and tie to the summary.</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>&lt;attribute_D_description&gt;</t>
+          <t>Billing rate change is supported by a governing-document amendment.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>&lt;attribute_D_toc_procedure&gt;</t>
+          <t>Inspect the governing-document file for an amendment matching any rate change.</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>&lt;attribute_E_description&gt;</t>
+          <t>Asset additions and retirements appear on the supporting schedule.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>&lt;attribute_E_toc_procedure&gt;</t>
+          <t>Compare asset additions and retirements listed on the supporting schedule.</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>&lt;attribute_F_description&gt;</t>
+          <t>Ownership-share percentages match the supporting reference file.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>&lt;attribute_F_toc_procedure&gt;</t>
+          <t>Recompute ownership-share percentages and agree to the supporting reference file.</t>
         </is>
       </c>
     </row>
